--- a/New folder/Email List.xlsx
+++ b/New folder/Email List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Competitor-Intelligence-Dashboard\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DBB1CE-D28F-49E7-9747-186FD3E7C293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9166151-791F-4EF8-BEFD-B136BA987BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2217EC6-5264-4912-89C2-A93DA417F83C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="28">
   <si>
     <t>Intl T&amp;D</t>
   </si>
@@ -120,6 +120,15 @@
   </si>
   <si>
     <t>Mayank Agarwal</t>
+  </si>
+  <si>
+    <t>fetch('https://competitor-intelligence-dashboard.onrender.com/api/digest-preview')
+.then(r=&gt;r.json())
+.then(d=&gt;{
+    var w = window.open();
+    w.document.write(d.previews[1].html);
+    w.document.close();
+});</t>
   </si>
 </sst>
 </file>
@@ -135,12 +144,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -207,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -216,17 +231,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D26039E-CE29-4C87-8CA3-76BCCC900E86}">
-  <dimension ref="C2:I14"/>
+  <dimension ref="C2:N19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="22.5546875" customWidth="1"/>
@@ -554,7 +574,7 @@
     <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
         <v>0</v>
@@ -575,30 +595,30 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="H3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
@@ -620,8 +640,11 @@
       <c r="I4" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="N4" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -636,8 +659,8 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="4" t="s">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -659,8 +682,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="5"/>
+    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C7" s="6"/>
       <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
@@ -680,8 +703,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="6" t="s">
+    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -703,8 +726,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="4" t="s">
+    <row r="9" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -726,7 +749,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C10" s="7"/>
       <c r="D10" s="1" t="s">
         <v>14</v>
@@ -747,29 +770,29 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C11" s="5"/>
-      <c r="D11" s="2" t="s">
+    <row r="11" spans="3:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C11" s="6"/>
+      <c r="D11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="4" t="s">
+    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -791,8 +814,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="3:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C13" s="5"/>
+    <row r="13" spans="3:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C13" s="6"/>
       <c r="D13" s="2" t="s">
         <v>20</v>
       </c>
@@ -812,7 +835,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
@@ -833,6 +856,38 @@
       </c>
       <c r="I14" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
